--- a/data/enos_excel/contingencias.xlsx
+++ b/data/enos_excel/contingencias.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/caritovillalba/Library/CloudStorage/Dropbox/Mac (2)/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F42D49B-6D23-424A-BBB3-4696CBD7B928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBDA13D-52A1-4BFE-BDF8-C37E7686BD2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="1600" windowWidth="27240" windowHeight="14780" xr2:uid="{522F0EB2-1E37-A54F-9E9E-E2F0D2661546}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{522F0EB2-1E37-A54F-9E9E-E2F0D2661546}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="52">
   <si>
     <t>ENOS</t>
   </si>
@@ -71,9 +70,6 @@
     <t>Suma de MONTO COBRADO2</t>
   </si>
   <si>
-    <t>15-oct</t>
-  </si>
-  <si>
     <t>IMBABURA</t>
   </si>
   <si>
@@ -113,9 +109,6 @@
     <t>PUERTO LOPEZ</t>
   </si>
   <si>
-    <t>16-oct</t>
-  </si>
-  <si>
     <t>GUAYAS</t>
   </si>
   <si>
@@ -125,9 +118,6 @@
     <t>VENDAVAL</t>
   </si>
   <si>
-    <t>22-oct</t>
-  </si>
-  <si>
     <t>AZUAY</t>
   </si>
   <si>
@@ -140,9 +130,6 @@
     <t>BOLIVAR</t>
   </si>
   <si>
-    <t>25-oct</t>
-  </si>
-  <si>
     <t>EL ORO</t>
   </si>
   <si>
@@ -179,21 +166,9 @@
     <t>BABAHOYO</t>
   </si>
   <si>
-    <t>25-sep</t>
-  </si>
-  <si>
     <t>LOJA</t>
   </si>
   <si>
-    <t>27-oct</t>
-  </si>
-  <si>
-    <t>28-oct</t>
-  </si>
-  <si>
-    <t>29-oct</t>
-  </si>
-  <si>
     <t>LAS NAVES</t>
   </si>
   <si>
@@ -213,6 +188,12 @@
   </si>
   <si>
     <t>Total general</t>
+  </si>
+  <si>
+    <t>MACHALA</t>
+  </si>
+  <si>
+    <t>RIOVERDE</t>
   </si>
 </sst>
 </file>
@@ -259,9 +240,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -597,14 +579,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8789C54A-D653-FD41-81CE-82E636699983}">
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="6" max="6" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.83203125" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -612,7 +594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -638,18 +620,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>10</v>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>46289</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" t="s">
         <v>12</v>
-      </c>
-      <c r="D4" t="s">
-        <v>13</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -657,19 +639,25 @@
       <c r="F4" s="1">
         <v>302.94</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1">
+        <v>302.94</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -678,70 +666,64 @@
         <v>302.94</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>10</v>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>46308</v>
       </c>
       <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>302.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1">
+        <v>605.88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>17</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1">
-        <v>605.88</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7">
+      <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8">
         <v>3</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F8" s="1">
         <v>908.81999999999994</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7" s="1">
-        <v>605.88</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" s="1">
-        <v>605.88</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -750,70 +732,70 @@
         <v>605.88</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>10</v>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>46308</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1">
+        <v>605.88</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" s="1">
+        <v>605.88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>302.94</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1">
+        <v>302.94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>302.94</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
-        <v>302.94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10">
-        <v>3</v>
-      </c>
-      <c r="F10" s="1">
-        <v>908.81999999999994</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-      <c r="H10" s="1">
-        <v>605.88</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" t="s">
-        <v>22</v>
-      </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11">
         <v>3</v>
@@ -828,324 +810,330 @@
         <v>908.81999999999994</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+      <c r="D12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
+      </c>
+      <c r="F12" s="1">
+        <v>908.81999999999994</v>
+      </c>
+      <c r="G12">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1">
+        <v>908.81999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
+        <v>46308</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13" s="1">
+        <v>9088.1999999999953</v>
+      </c>
+      <c r="G13">
+        <v>25</v>
+      </c>
+      <c r="H13" s="1">
+        <v>7573.4999999999955</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>46310</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1">
+        <v>4241.16</v>
+      </c>
+      <c r="G14">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1">
+        <v>4241.16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15" s="1">
+        <v>303.99</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>303.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
+        <v>46316</v>
+      </c>
+      <c r="B16" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" s="1">
+        <v>302.94</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" s="1">
+        <v>302.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>158</v>
+      </c>
+      <c r="F17" s="1">
+        <v>48030.419999999976</v>
+      </c>
+      <c r="G17">
+        <v>103</v>
+      </c>
+      <c r="H17" s="1">
+        <v>31310.97000000007</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B18" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1">
+        <v>3951.869999999999</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1519.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>489</v>
+      </c>
+      <c r="F19" s="1">
+        <v>148137.66000000082</v>
+      </c>
+      <c r="G19">
+        <v>238</v>
+      </c>
+      <c r="H19" s="1">
+        <v>72099.720000000234</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1211.76</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20" s="1">
+        <v>908.81999999999994</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A21" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21">
+        <v>293</v>
+      </c>
+      <c r="F21" s="1">
+        <v>88761.420000000362</v>
+      </c>
+      <c r="G21">
+        <v>281</v>
+      </c>
+      <c r="H21" s="1">
+        <v>85126.140000000334</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A22" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22">
+        <v>33</v>
+      </c>
+      <c r="F22" s="1">
+        <v>10031.669999999995</v>
+      </c>
+      <c r="G22">
+        <v>32</v>
+      </c>
+      <c r="H22" s="1">
+        <v>9727.6799999999948</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B23" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12">
-        <v>30</v>
-      </c>
-      <c r="F12" s="1">
-        <v>9088.1999999999953</v>
-      </c>
-      <c r="G12">
-        <v>23</v>
-      </c>
-      <c r="H12" s="1">
-        <v>6967.6199999999963</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13">
-        <v>14</v>
-      </c>
-      <c r="F13" s="1">
-        <v>4241.16</v>
-      </c>
-      <c r="G13">
-        <v>14</v>
-      </c>
-      <c r="H13" s="1">
-        <v>4241.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>303.99</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="1">
-        <v>303.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>302.94</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="1">
-        <v>302.94</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16">
-        <v>158</v>
-      </c>
-      <c r="F16" s="1">
-        <v>48030.419999999976</v>
-      </c>
-      <c r="G16">
-        <v>74</v>
-      </c>
-      <c r="H16" s="1">
-        <v>22495.260000000024</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>33</v>
-      </c>
-      <c r="B17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E17">
-        <v>13</v>
-      </c>
-      <c r="F17" s="1">
-        <v>3951.869999999999</v>
-      </c>
-      <c r="G17">
-        <v>4</v>
-      </c>
-      <c r="H17" s="1">
-        <v>1215.96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>33</v>
-      </c>
-      <c r="B18" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23">
+        <v>3</v>
+      </c>
+      <c r="F23" s="1">
+        <v>911.97</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+      <c r="H23" s="1">
+        <v>911.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" t="s">
         <v>38</v>
       </c>
-      <c r="D18" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18">
-        <v>489</v>
-      </c>
-      <c r="F18" s="1">
-        <v>148137.66000000082</v>
-      </c>
-      <c r="G18">
-        <v>178</v>
-      </c>
-      <c r="H18" s="1">
-        <v>53923.320000000102</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" t="s">
-        <v>39</v>
-      </c>
-      <c r="D19" t="s">
-        <v>16</v>
-      </c>
-      <c r="E19">
-        <v>4</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1211.76</v>
-      </c>
-      <c r="G19">
-        <v>3</v>
-      </c>
-      <c r="H19" s="1">
-        <v>908.81999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20">
-        <v>293</v>
-      </c>
-      <c r="F20" s="1">
-        <v>88761.420000000362</v>
-      </c>
-      <c r="G20">
-        <v>268</v>
-      </c>
-      <c r="H20" s="1">
-        <v>81187.920000000304</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21">
-        <v>33</v>
-      </c>
-      <c r="F21" s="1">
-        <v>10031.669999999995</v>
-      </c>
-      <c r="G21">
-        <v>31</v>
-      </c>
-      <c r="H21" s="1">
-        <v>9423.6899999999951</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" t="s">
-        <v>16</v>
-      </c>
-      <c r="E22">
-        <v>3</v>
-      </c>
-      <c r="F22" s="1">
-        <v>911.97</v>
-      </c>
-      <c r="G22">
-        <v>3</v>
-      </c>
-      <c r="H22" s="1">
-        <v>911.97</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>33</v>
-      </c>
-      <c r="B23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>303.99</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B24" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -1153,25 +1141,19 @@
       <c r="F24" s="1">
         <v>303.99</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>303.99</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>33</v>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" s="2">
+        <v>46320</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E25">
         <v>1</v>
@@ -1186,168 +1168,174 @@
         <v>303.99</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A26" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" t="s">
+        <v>41</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+      <c r="F26" s="1">
+        <v>303.99</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" s="1">
+        <v>303.99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27">
+        <v>102</v>
+      </c>
+      <c r="F27" s="1">
+        <v>30911.429999999978</v>
+      </c>
+      <c r="G27">
+        <v>80</v>
+      </c>
+      <c r="H27" s="1">
+        <v>24245.700000000004</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" s="2">
+        <v>46320</v>
+      </c>
+      <c r="B28" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28" s="1">
+        <v>607.98</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" s="1">
+        <v>303.99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B29" t="s">
         <v>33</v>
       </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26">
-        <v>102</v>
-      </c>
-      <c r="F26" s="1">
-        <v>30911.429999999978</v>
-      </c>
-      <c r="G26">
-        <v>68</v>
-      </c>
-      <c r="H26" s="1">
-        <v>20609.370000000017</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27" s="1">
-        <v>607.98</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>303.99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>302.94</v>
-      </c>
-      <c r="G28">
-        <v>1</v>
-      </c>
-      <c r="H28" s="1">
-        <v>302.94</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29" t="s">
-        <v>25</v>
-      </c>
       <c r="C29" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29">
+        <v>528</v>
+      </c>
+      <c r="F29" s="1">
+        <v>159952.32000000091</v>
+      </c>
+      <c r="G29">
+        <v>36</v>
+      </c>
+      <c r="H29" s="1">
+        <v>10905.839999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>37</v>
+      </c>
+      <c r="D30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30">
         <v>9</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F30" s="1">
         <v>2735.91</v>
       </c>
-      <c r="G29">
+      <c r="G30">
         <v>8</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H30" s="1">
         <v>2431.92</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" s="2">
+        <v>46322</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31">
         <v>5</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F31" s="1">
         <v>1519.95</v>
       </c>
-      <c r="G30">
-        <v>2</v>
-      </c>
-      <c r="H30" s="1">
-        <v>607.98</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" t="s">
-        <v>37</v>
-      </c>
-      <c r="C31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" t="s">
-        <v>16</v>
-      </c>
-      <c r="E31">
-        <v>528</v>
-      </c>
-      <c r="F31" s="1">
-        <v>159952.32000000091</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>50</v>
+      <c r="G31">
+        <v>4</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1215.96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A32" s="2">
+        <v>46323</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -1356,18 +1344,18 @@
         <v>1823.94</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>50</v>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>46323</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C33" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -1376,18 +1364,18 @@
         <v>303.99</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>50</v>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
+        <v>46323</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -1396,18 +1384,18 @@
         <v>303.99</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>50</v>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
+        <v>46323</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -1416,21 +1404,81 @@
         <v>2127.9300000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>57</v>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A36" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B36" t="s">
+        <v>30</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" t="s">
+        <v>15</v>
       </c>
       <c r="E36">
-        <v>1720</v>
+        <v>178</v>
       </c>
       <c r="F36" s="1">
-        <v>521322.45000000246</v>
-      </c>
-      <c r="G36">
-        <v>692</v>
-      </c>
-      <c r="H36" s="1">
-        <v>209776.23000000071</v>
+        <v>54110.219999999936</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A37" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B37" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" t="s">
+        <v>33</v>
+      </c>
+      <c r="D37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37">
+        <v>1128</v>
+      </c>
+      <c r="F37" s="1">
+        <v>341716.32000000228</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A38" s="2">
+        <v>46325</v>
+      </c>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38">
+        <v>79</v>
+      </c>
+      <c r="F38" s="1">
+        <v>24015.210000000032</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39">
+        <v>3105</v>
+      </c>
+      <c r="F39" s="1">
+        <v>941164.19999993709</v>
+      </c>
+      <c r="G39">
+        <v>849</v>
+      </c>
+      <c r="H39" s="1">
+        <v>257373.51000000088</v>
       </c>
     </row>
   </sheetData>
